--- a/_FACTORY/_LIGNES/_MAYENNE/B3_DISTRACTEURS/B3_THEME.xlsx
+++ b/_FACTORY/_LIGNES/_MAYENNE/B3_DISTRACTEURS/B3_THEME.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>[non trouvé dans glossaire — vérifier source]</t>
+          <t>Trois étapes séquentielles de l'entonnoir B3 (génération, audit, optimisation).</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr"/>
@@ -932,10 +932,14 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>[non trouvé dans glossaire — vérifier source]</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr"/>
+          <t>Comportement obligatoire de signalement des opportunités de réduction de tokens avant chaque action ou tool call.</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>[RULE-TOKEN-MONITOR-001] CLAUDE SIGNALE CHAQUE OPPORTUNITÉ TOKEN — comportement obligatoire, tous contextes.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -969,43 +973,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>MANQUANT</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>PASS_FUNNEL — présent dans config step mais absent du glossaire</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>→ Ajouter dans glossaire_documentaire_factory.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>MANQUANT</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>TOKEN_OPTIMIZATION_MONITORING — présent dans config step mais absent du glossaire</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>→ Ajouter dans glossaire_documentaire_factory.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-19</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Aucune alerte automatique — vérification manuelle recommandée à chaque étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -1013,8 +990,8 @@
   <mergeCells count="5">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
